--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484214_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484214_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7482</v>
+        <v>5.8115</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2389</v>
+        <v>2.1466</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5093</v>
+        <v>3.665</v>
       </c>
       <c r="G2" t="n">
         <v>4.5502</v>
@@ -610,13 +610,13 @@
         <v>4.4929</v>
       </c>
       <c r="S2" t="n">
-        <v>4.117</v>
+        <v>2.1804</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7131</v>
+        <v>1.6208</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4039</v>
+        <v>0.5596</v>
       </c>
       <c r="V2" t="n">
         <v>-1.505</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6639</v>
+        <v>3.3883</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2587</v>
+        <v>1.8742</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4052</v>
+        <v>1.5141</v>
       </c>
       <c r="G3" t="n">
         <v>0.3901</v>
@@ -688,13 +688,13 @@
         <v>3.1255</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9696</v>
+        <v>0.694</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1145</v>
+        <v>0.7299</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1448</v>
+        <v>-0.0359</v>
       </c>
       <c r="V3" t="n">
         <v>0.1554</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>È. ARUMÍ COLOM</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5816</v>
+        <v>1.8583</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0392</v>
+        <v>-1.7547</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6207</v>
+        <v>3.613</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8209</v>
+        <v>1.9135</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1468</v>
+        <v>-0.5828</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6741</v>
+        <v>2.4962</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0819</v>
+        <v>2.4872</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0819</v>
+        <v>0.1253</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3618</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7391</v>
+        <v>-0.5737</v>
       </c>
       <c r="N4" t="n">
-        <v>0.065</v>
+        <v>-0.7081</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6741</v>
+        <v>0.1344</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-5.8603</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>3.5162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4347</v>
+        <v>0.152</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>0.3998</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3137</v>
+        <v>-0.2477</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1369</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.9183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2437</v>
+        <v>1.208</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.988</v>
+        <v>1.2003</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2318</v>
+        <v>0.0078</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9135</v>
+        <v>0.1122</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5828</v>
+        <v>0.166</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4962</v>
+        <v>-0.0539</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4872</v>
+        <v>1.4202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1253</v>
+        <v>0.7994</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3618</v>
+        <v>0.6208</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5737</v>
+        <v>-1.3081</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7081</v>
+        <v>-0.6334</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1344</v>
+        <v>-0.6747</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.8603</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5162</v>
+        <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4626</v>
+        <v>1.2134</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8335</v>
+        <v>0.7567</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.629</v>
+        <v>0.4566</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1369</v>
+        <v>-1.4849</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9183</v>
+        <v>-1.4849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>È. ARUMÍ COLOM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0602</v>
+        <v>0.92</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2703</v>
+        <v>0.163</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2101</v>
+        <v>0.7569</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1122</v>
+        <v>0.8209</v>
       </c>
       <c r="H6" t="n">
-        <v>0.166</v>
+        <v>0.1468</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0539</v>
+        <v>0.6741</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4202</v>
+        <v>0.0819</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7994</v>
+        <v>0.0819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3081</v>
+        <v>0.7391</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6334</v>
+        <v>0.065</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6747</v>
+        <v>0.6741</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0655</v>
+        <v>-0.0963</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1732</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2388</v>
+        <v>-0.1775</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4849</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0915</v>
+        <v>-1.3948</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1378</v>
+        <v>-1.4412</v>
       </c>
       <c r="F7" t="n">
         <v>0.0464</v>
@@ -1000,10 +1000,10 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4925</v>
+        <v>0.1892</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4925</v>
+        <v>0.1892</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9178</v>
+        <v>-1.6023</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3111</v>
+        <v>-3.3493</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6067</v>
+        <v>1.747</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0766</v>
+        <v>-1.7841</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0517</v>
+        <v>-1.4469</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0249</v>
+        <v>-0.3371</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4407</v>
+        <v>-1.1548</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8199</v>
+        <v>-1.2229</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6208</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3641</v>
+        <v>-0.6293</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7682</v>
+        <v>-0.2241</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4041</v>
+        <v>-0.4052</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2713</v>
+        <v>0.8742</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8778</v>
+        <v>0.7905</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6065</v>
+        <v>0.0838</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0936</v>
+        <v>0.089</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3708</v>
+        <v>0.1438</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9861</v>
+        <v>-2.0945</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3315</v>
+        <v>-5.4127</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3454</v>
+        <v>3.3182</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5233</v>
@@ -1156,13 +1156,13 @@
         <v>3.1255</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4841</v>
+        <v>1.3756</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2493</v>
+        <v>1.1681</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2348</v>
+        <v>0.2075</v>
       </c>
       <c r="V9" t="n">
         <v>0.7647</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4431</v>
+        <v>-2.1588</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6843</v>
+        <v>-1.7156</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2412</v>
+        <v>-0.4433</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1168</v>
+        <v>1.0766</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.0517</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0541</v>
+        <v>1.0249</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7768</v>
+        <v>1.4407</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6958</v>
+        <v>0.8199</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>0.6208</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8935</v>
+        <v>-0.3641</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7585</v>
+        <v>-0.7682</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.135</v>
+        <v>0.4041</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5395</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4458</v>
+        <v>0.4733</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3218</v>
+        <v>-0.4431</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>-2.0936</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5545</v>
+        <v>-2.3708</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4462</v>
+        <v>-2.9177</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0571</v>
+        <v>-2.8865</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6109</v>
+        <v>-0.0311</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7841</v>
+        <v>-0.1168</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4469</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3371</v>
+        <v>-0.0541</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1548</v>
+        <v>0.7768</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2229</v>
+        <v>0.6958</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6293</v>
+        <v>-0.8935</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2241</v>
+        <v>-0.7585</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4052</v>
+        <v>-0.135</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0303</v>
+        <v>0.293</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2436</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0524</v>
+        <v>0.0495</v>
       </c>
       <c r="V11" t="n">
-        <v>0.089</v>
+        <v>-0.5545</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1438</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4129</v>
+        <v>3.018000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.7811</v>
+        <v>-11.1759</v>
       </c>
       <c r="F12" t="n">
-        <v>14.1941</v>
+        <v>14.194</v>
       </c>
       <c r="G12" t="n">
-        <v>5.4413</v>
+        <v>5.441300000000002</v>
       </c>
       <c r="H12" t="n">
         <v>6.1153</v>
@@ -1390,13 +1390,13 @@
         <v>23.4412</v>
       </c>
       <c r="S12" t="n">
-        <v>6.300599999999999</v>
+        <v>6.9058</v>
       </c>
       <c r="T12" t="n">
-        <v>5.8479</v>
+        <v>6.4531</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4528999999999999</v>
+        <v>0.4527999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.492</v>
@@ -1405,7 +1405,7 @@
         <v>2.9398</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.431900000000001</v>
+        <v>-5.4319</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.186500000000001</v>
+        <v>8.026199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2946</v>
+        <v>6.0812</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8919</v>
+        <v>1.945</v>
       </c>
       <c r="G13" t="n">
         <v>4.8168</v>
@@ -1468,13 +1468,13 @@
         <v>3.9069</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2757</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4254</v>
+        <v>0.212</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1497</v>
+        <v>-1.0966</v>
       </c>
       <c r="V13" t="n">
         <v>1.1638</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4914</v>
+        <v>1.5347</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4394</v>
+        <v>-0.5717</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0519</v>
+        <v>2.1064</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7349</v>
@@ -1546,13 +1546,13 @@
         <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2029</v>
+        <v>0.2463</v>
       </c>
       <c r="T14" t="n">
-        <v>1.175</v>
+        <v>0.1638</v>
       </c>
       <c r="U14" t="n">
-        <v>0.028</v>
+        <v>0.0824</v>
       </c>
       <c r="V14" t="n">
         <v>1.8279</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8258</v>
+        <v>0.6319</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3009</v>
+        <v>-0.1297</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5249</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2314</v>
+        <v>-0.2319</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8655</v>
+        <v>-0.272</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.634</v>
+        <v>0.0401</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3298</v>
+        <v>0.3922</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2893</v>
+        <v>0.3517</v>
       </c>
       <c r="L15" t="n">
         <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0984</v>
+        <v>-0.6241</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4239</v>
+        <v>-0.6237</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6745</v>
+        <v>-0.0004</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4028</v>
+        <v>-0.4533</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9245</v>
+        <v>-0.0997</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5218</v>
+        <v>-0.3536</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3869</v>
+        <v>-0.8317</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3869</v>
+        <v>-1.3862</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.317</v>
+        <v>0.2227</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6353</v>
+        <v>-0.7984</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9522</v>
+        <v>1.0211</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2319</v>
+        <v>-0.212</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.272</v>
+        <v>-1.79</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0401</v>
+        <v>1.578</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3922</v>
+        <v>0.8317</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3517</v>
+        <v>-1.0169</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>1.8486</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6241</v>
+        <v>-1.0437</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6237</v>
+        <v>-0.7731</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0004</v>
+        <v>-0.2706</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1255</v>
+        <v>3.3208</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7682</v>
+        <v>-1.2099</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6052</v>
+        <v>-0.5632</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.163</v>
+        <v>-0.6468</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>0.8865</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3862</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1039</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5062</v>
+        <v>-0.4069</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4023</v>
+        <v>0.4963</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.212</v>
+        <v>0.2314</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.79</v>
+        <v>0.8655</v>
       </c>
       <c r="I17" t="n">
-        <v>1.578</v>
+        <v>-0.634</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8317</v>
+        <v>1.3298</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0169</v>
+        <v>1.2893</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8486</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0437</v>
+        <v>-1.0984</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7731</v>
+        <v>-0.4239</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2706</v>
+        <v>-0.6745</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3208</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5364</v>
+        <v>-0.3336</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.271</v>
+        <v>0.2167</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2655</v>
+        <v>-0.5503</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>0.3869</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9386</v>
+        <v>-0.0868</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0801</v>
+        <v>-2.4734</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1414</v>
+        <v>2.3865</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3779</v>
@@ -1858,13 +1858,13 @@
         <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.237</v>
+        <v>-0.3852</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1801</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4502</v>
+        <v>-0.205</v>
       </c>
       <c r="V18" t="n">
         <v>0.3321</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8215</v>
+        <v>-1.5918</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5409</v>
+        <v>-4.25</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7194</v>
+        <v>2.6582</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4481</v>
+        <v>-2.8263</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.165</v>
+        <v>-1.9491</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2831</v>
+        <v>-0.8772</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1639</v>
+        <v>-0.9591</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3888</v>
+        <v>-0.4874</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5527</v>
+        <v>-0.4718</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2842</v>
+        <v>-1.8672</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5538</v>
+        <v>-1.4617</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>-0.4054</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>4.8836</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0061</v>
+        <v>-1.6054</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5531</v>
+        <v>-0.5831</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5591</v>
+        <v>-1.0223</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1398</v>
+        <v>-1.6005</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7397</v>
+        <v>-1.3353</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4</v>
+        <v>-0.2652</v>
       </c>
       <c r="G20" t="n">
         <v>-1.206</v>
@@ -2014,13 +2014,13 @@
         <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.465</v>
+        <v>0.0743</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3631</v>
+        <v>0.0413</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1018</v>
+        <v>0.033</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6642</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7806</v>
+        <v>-1.8072</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0589</v>
+        <v>-2.7432</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2783</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8263</v>
+        <v>-0.4481</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9491</v>
+        <v>-0.165</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8772</v>
+        <v>-0.2831</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9591</v>
+        <v>-0.1639</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4874</v>
+        <v>0.3888</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4718</v>
+        <v>-0.5527</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8672</v>
+        <v>-0.2842</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4617</v>
+        <v>-0.5538</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4054</v>
+        <v>0.2696</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>4.8836</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7943</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.392</v>
+        <v>0.3508</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4023</v>
+        <v>-0.3426</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9665</v>
+        <v>-2.737</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1381</v>
+        <v>-1.9359</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8284</v>
+        <v>-0.8012</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1428</v>
@@ -2170,13 +2170,13 @@
         <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4331</v>
+        <v>-0.2036</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1816</v>
+        <v>0.0207</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2515</v>
+        <v>-0.2242</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4826</v>
+        <v>-4.4203</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5297</v>
+        <v>-5.6308</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0471</v>
+        <v>1.2105</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3099</v>
@@ -2248,13 +2248,13 @@
         <v>3.5162</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9421</v>
+        <v>-0.8798</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0689</v>
+        <v>-0.0322</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0109</v>
+        <v>-0.8475</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8865</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.412799999999999</v>
+        <v>-1.738700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.194</v>
+        <v>-14.1941</v>
       </c>
       <c r="F24" t="n">
-        <v>11.781</v>
+        <v>12.4552</v>
       </c>
       <c r="G24" t="n">
         <v>-5.441599999999998</v>
@@ -2296,10 +2296,10 @@
         <v>-6.115500000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6740999999999999</v>
+        <v>0.6740999999999998</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2681</v>
+        <v>4.268099999999999</v>
       </c>
       <c r="K24" t="n">
         <v>2.9148</v>
@@ -2326,13 +2326,13 @@
         <v>30.2782</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.300799999999999</v>
+        <v>-5.626599999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4527999999999996</v>
+        <v>-0.453</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.847799999999999</v>
+        <v>-5.1735</v>
       </c>
       <c r="V24" t="n">
         <v>2.492</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484214_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484214_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0084</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2856</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.9183</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-1.4849</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>È. ARUMÍ COLOM</t>
+          <t>E. ARUMI COLOM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SOY BASSOLS</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,55 +985,55 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3948</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4412</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0464</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.998</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.998</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6536</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6536</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3443</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3443</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1892</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1892</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>M. SOY BASSOLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6023</v>
+        <v>-1.3948</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3493</v>
+        <v>-1.4412</v>
       </c>
       <c r="F8" t="n">
-        <v>1.747</v>
+        <v>0.0464</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7841</v>
+        <v>-0.998</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4469</v>
+        <v>-0.998</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3371</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1548</v>
+        <v>-0.6536</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2229</v>
+        <v>-0.6536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06809999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6293</v>
+        <v>-0.3443</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2241</v>
+        <v>-0.3443</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4052</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8742</v>
+        <v>0.1892</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7905</v>
+        <v>0.1892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0838</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1438</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0945</v>
+        <v>-1.6023</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4127</v>
+        <v>-3.3493</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3182</v>
+        <v>1.747</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5233</v>
+        <v>-1.7841</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9179</v>
+        <v>-1.4469</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4412</v>
+        <v>-0.3371</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2982</v>
+        <v>-1.1548</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6027</v>
+        <v>-1.2229</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9009</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2251</v>
+        <v>-0.6293</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3152</v>
+        <v>-0.2241</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5403</v>
+        <v>-0.4052</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.7115</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.837</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1255</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3756</v>
+        <v>0.8742</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1681</v>
+        <v>0.7905</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2075</v>
+        <v>0.0838</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7647</v>
+        <v>0.089</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>-0.0549</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2102</v>
+        <v>0.1438</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1588</v>
+        <v>-2.0945</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7156</v>
+        <v>-5.4127</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4433</v>
+        <v>3.3182</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0766</v>
+        <v>-0.5233</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0517</v>
+        <v>1.9179</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0249</v>
+        <v>-2.4412</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4407</v>
+        <v>-0.2982</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8199</v>
+        <v>1.6027</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6208</v>
+        <v>-1.9009</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3641</v>
+        <v>-0.2251</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7682</v>
+        <v>0.3152</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4041</v>
+        <v>-0.5403</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-6.837</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7348</v>
+        <v>3.1255</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0303</v>
+        <v>1.3756</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4733</v>
+        <v>1.1681</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4431</v>
+        <v>0.2075</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0936</v>
+        <v>0.7647</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3708</v>
+        <v>0.2102</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9177</v>
+        <v>-2.4658</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8865</v>
+        <v>-2.0226</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0311</v>
+        <v>-0.4433</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1168</v>
+        <v>0.7696</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.2553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0541</v>
+        <v>1.0249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7768</v>
+        <v>1.1337</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6958</v>
+        <v>0.5129</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>0.6208</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8935</v>
+        <v>-0.3641</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7585</v>
+        <v>-0.7682</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.135</v>
+        <v>0.4041</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5395</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S11" t="n">
-        <v>0.293</v>
+        <v>0.0303</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2436</v>
+        <v>0.4733</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0495</v>
+        <v>-0.4431</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5545</v>
+        <v>-2.0936</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>-2.3708</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,1004 +1400,1393 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.018000000000001</v>
+        <v>-2.9177</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.1759</v>
+        <v>-2.8865</v>
       </c>
       <c r="F12" t="n">
-        <v>14.194</v>
+        <v>-0.0311</v>
       </c>
       <c r="G12" t="n">
-        <v>5.441300000000002</v>
+        <v>-0.1168</v>
       </c>
       <c r="H12" t="n">
-        <v>6.1153</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6740999999999997</v>
+        <v>-0.0541</v>
       </c>
       <c r="J12" t="n">
-        <v>9.7095</v>
+        <v>0.7768</v>
       </c>
       <c r="K12" t="n">
-        <v>9.0303</v>
+        <v>0.6958</v>
       </c>
       <c r="L12" t="n">
-        <v>0.679</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.2679</v>
+        <v>-0.8935</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.9148</v>
+        <v>-0.7585</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3531</v>
+        <v>-0.135</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.8371</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q12" t="n">
-        <v>-30.2782</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
-        <v>23.4412</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>6.9058</v>
+        <v>0.293</v>
       </c>
       <c r="T12" t="n">
-        <v>6.4531</v>
+        <v>0.2436</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4527999999999999</v>
+        <v>0.0495</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.492</v>
+        <v>-0.5545</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9398</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.4319</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.026199999999999</v>
+        <v>3.018000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0812</v>
+        <v>-11.1759</v>
       </c>
       <c r="F13" t="n">
-        <v>1.945</v>
+        <v>14.194</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8168</v>
+        <v>5.441300000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3354</v>
+        <v>6.115299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4814</v>
+        <v>-0.6740999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4049</v>
+        <v>9.7095</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1366</v>
+        <v>9.0303</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2683</v>
+        <v>0.679</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.588</v>
+        <v>-4.2679</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8012</v>
+        <v>-2.9148</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2132</v>
+        <v>-1.3531</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9301</v>
+        <v>-6.8371</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-30.2782</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9069</v>
+        <v>23.4412</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8846000000000001</v>
+        <v>6.9058</v>
       </c>
       <c r="T13" t="n">
-        <v>0.212</v>
+        <v>6.4531</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0966</v>
+        <v>0.4527999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1638</v>
+        <v>-2.492</v>
       </c>
       <c r="W13" t="n">
-        <v>1.441</v>
+        <v>2.9398</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-5.4319</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5347</v>
+        <v>6.4982</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5717</v>
+        <v>4.5533</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1064</v>
+        <v>1.945</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7349</v>
+        <v>3.2889</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1289</v>
+        <v>1.4145</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8638</v>
+        <v>1.8745</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6987</v>
+        <v>3.8769</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6178</v>
+        <v>3.2157</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0809</v>
+        <v>0.6613</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4336</v>
+        <v>-0.588</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4889</v>
+        <v>-1.8012</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9447</v>
+        <v>1.2132</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1953</v>
+        <v>2.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1255</v>
+        <v>3.9069</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2463</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1638</v>
+        <v>0.212</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0824</v>
+        <v>-1.0966</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8279</v>
+        <v>1.1638</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>1.441</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6319</v>
+        <v>1.5347</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1297</v>
+        <v>-0.5717</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7616000000000001</v>
+        <v>2.1064</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2319</v>
+        <v>-0.7349</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.272</v>
+        <v>0.1289</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0401</v>
+        <v>-0.8638</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3922</v>
+        <v>0.6987</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3517</v>
+        <v>0.6178</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6241</v>
+        <v>-1.4336</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6237</v>
+        <v>-0.4889</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0004</v>
+        <v>-0.9447</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
         <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4533</v>
+        <v>0.2463</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0997</v>
+        <v>0.1638</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3536</v>
+        <v>0.0824</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8317</v>
+        <v>1.8279</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>1.4959</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3862</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2227</v>
+        <v>1.5279</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7984</v>
+        <v>1.5279</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0211</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.212</v>
+        <v>1.5279</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.79</v>
+        <v>0.921</v>
       </c>
       <c r="I16" t="n">
-        <v>1.578</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8317</v>
+        <v>1.5279</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0169</v>
+        <v>0.921</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8486</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7731</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2706</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3208</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2099</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5632</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.2279</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4069</v>
+        <v>1.2279</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4963</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2314</v>
+        <v>1.2279</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8655</v>
+        <v>1.2279</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.634</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3298</v>
+        <v>1.2279</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2893</v>
+        <v>1.2279</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0984</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4239</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3336</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2167</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5503</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0868</v>
+        <v>0.6319</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4734</v>
+        <v>-0.1297</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3865</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3779</v>
+        <v>-0.2319</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5421</v>
+        <v>-0.272</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8358</v>
+        <v>0.0401</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2933</v>
+        <v>0.3922</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9184</v>
+        <v>0.3517</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3748</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.6241</v>
       </c>
       <c r="N18" t="n">
         <v>-0.6237</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5391</v>
+        <v>-0.0004</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3852</v>
+        <v>-0.4533</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1801</v>
+        <v>-0.0997</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.205</v>
+        <v>-0.3536</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>-0.8317</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>-1.3862</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5918</v>
+        <v>0.607</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.25</v>
+        <v>0.607</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6582</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8263</v>
+        <v>0.607</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9491</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8772</v>
+        <v>0.607</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9591</v>
+        <v>0.607</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4874</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4718</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8672</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4617</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4054</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.8836</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6054</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5831</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0223</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6005</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3353</v>
+        <v>-0.4069</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2652</v>
+        <v>0.4963</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.206</v>
+        <v>0.2314</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3953</v>
+        <v>0.8655</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1893</v>
+        <v>-0.634</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0224</v>
+        <v>1.3298</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5718</v>
+        <v>1.2893</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5942</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2283</v>
+        <v>-1.0984</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8235</v>
+        <v>-0.4239</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4049</v>
+        <v>-0.6745</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0743</v>
+        <v>-0.3336</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0413</v>
+        <v>0.2167</v>
       </c>
       <c r="U20" t="n">
-        <v>0.033</v>
+        <v>-0.5503</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6642</v>
+        <v>0.3869</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8072</v>
+        <v>-0.0868</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7432</v>
+        <v>-2.4734</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9360000000000001</v>
+        <v>2.3865</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4481</v>
+        <v>-2.3779</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.165</v>
+        <v>-1.5421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2831</v>
+        <v>-0.8358</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1639</v>
+        <v>-2.2933</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3888</v>
+        <v>-0.9184</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5527</v>
+        <v>-1.3748</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2842</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5538</v>
+        <v>-0.6237</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2696</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.3852</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3508</v>
+        <v>-0.1801</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3426</v>
+        <v>-0.205</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. ROSA BEJARANO</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.737</v>
+        <v>-0.3843</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9359</v>
+        <v>-1.4054</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8012</v>
+        <v>1.0211</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1428</v>
+        <v>-0.819</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9294</v>
+        <v>-1.79</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2134</v>
+        <v>0.971</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9798</v>
+        <v>0.2247</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3684</v>
+        <v>-1.0169</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>1.2416</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.163</v>
+        <v>-1.0437</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2978</v>
+        <v>-0.7731</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1348</v>
+        <v>-0.2706</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>3.3208</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2036</v>
+        <v>-1.2099</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0207</v>
+        <v>-0.5632</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2242</v>
+        <v>-0.6468</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4203</v>
+        <v>-1.5918</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6308</v>
+        <v>-4.25</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2105</v>
+        <v>2.6582</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3099</v>
+        <v>-2.8263</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4024</v>
+        <v>-1.9491</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0926</v>
+        <v>-0.8772</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0155</v>
+        <v>-0.9591</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2433</v>
+        <v>-0.4874</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2278</v>
+        <v>-0.4718</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2943</v>
+        <v>-1.8672</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1591</v>
+        <v>-1.4617</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1352</v>
+        <v>-0.4054</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.8603</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>3.5162</v>
+        <v>4.8836</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8798</v>
+        <v>-1.6054</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0322</v>
+        <v>-0.5831</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8475</v>
+        <v>-1.0223</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8865</v>
+        <v>0.8865</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0.2224</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1638</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.738700000000001</v>
+        <v>-1.6005</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.1941</v>
+        <v>-1.3353</v>
       </c>
       <c r="F24" t="n">
+        <v>-0.2652</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.206</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.3953</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1893</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.5718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.2283</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.8235</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F. ALVAREZ BACO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.8072</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.7432</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.4481</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.2831</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.1639</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2842</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.5538</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.3426</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>O. ROSA BEJARANO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.737</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.9359</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.8012</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.1428</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.9294</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.2134</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.9798</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.163</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.2978</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2036</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.2242</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P. GONZALEZ BRUMOS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.6482</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.8588</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.2105</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.5378</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.6304</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.0926</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.2435</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-2.4713</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.2278</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.2943</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.1591</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-5.8603</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.5162</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.8798</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.8475</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484214_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.738800000000002</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-14.1942</v>
+      </c>
+      <c r="F28" t="n">
         <v>12.4552</v>
       </c>
-      <c r="G24" t="n">
-        <v>-5.441599999999998</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-6.115500000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.6740999999999998</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.268099999999999</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.9148</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="G28" t="n">
+        <v>-5.4416</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-6.1155</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.2679</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.914800000000001</v>
+      </c>
+      <c r="L28" t="n">
         <v>1.3533</v>
       </c>
-      <c r="M24" t="n">
-        <v>-9.7094</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="M28" t="n">
+        <v>-9.709399999999999</v>
+      </c>
+      <c r="N28" t="n">
         <v>-9.0304</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-0.6789999999999998</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P28" t="n">
         <v>6.836899999999999</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q28" t="n">
         <v>-23.4409</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>30.2782</v>
       </c>
-      <c r="S24" t="n">
-        <v>-5.626599999999999</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-0.453</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="S28" t="n">
+        <v>-5.6266</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.4529999999999999</v>
+      </c>
+      <c r="U28" t="n">
         <v>-5.1735</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V28" t="n">
         <v>2.492</v>
       </c>
-      <c r="W24" t="n">
-        <v>5.431999999999999</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="W28" t="n">
+        <v>5.432</v>
+      </c>
+      <c r="X28" t="n">
         <v>-2.9398</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
